--- a/development/one_file_rosetta_output/SP112777_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP112777_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>58</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,9 +576,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,9 +635,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4">
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -676,9 +694,12 @@
         </is>
       </c>
       <c r="D6" s="4">
+        <v>58</v>
+      </c>
+      <c r="E6" s="4">
         <v>5</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -734,7 +755,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -760,9 +784,12 @@
         </is>
       </c>
       <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -823,9 +850,12 @@
         </is>
       </c>
       <c r="D9" s="4">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -888,7 +918,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -916,7 +949,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -987,7 +1023,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1013,9 +1052,12 @@
         </is>
       </c>
       <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1069,9 +1111,12 @@
         </is>
       </c>
       <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
         <v>2</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1125,9 +1170,12 @@
         </is>
       </c>
       <c r="D15" s="4">
+        <v>4</v>
+      </c>
+      <c r="E15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1181,9 +1229,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>4</v>
+      </c>
+      <c r="E16" s="4">
         <v>2</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1237,9 +1288,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4">
         <v>3</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1295,7 +1349,10 @@
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1323,7 +1380,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1386,7 +1446,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1447,9 +1510,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>8</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1503,9 +1569,12 @@
         </is>
       </c>
       <c r="D22" s="4">
+        <v>8</v>
+      </c>
+      <c r="E22" s="4">
         <v>2</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1559,9 +1628,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>6</v>
+      </c>
+      <c r="E23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1615,9 +1687,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>6</v>
+      </c>
+      <c r="E24" s="4">
         <v>2</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1671,9 +1746,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>6</v>
+      </c>
+      <c r="E25" s="4">
         <v>3</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1727,9 +1805,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>6</v>
+      </c>
+      <c r="E26" s="4">
         <v>4</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1783,9 +1864,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>6</v>
+      </c>
+      <c r="E27" s="4">
         <v>5</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1839,9 +1923,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1902,9 +1989,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1932,7 +2022,10 @@
       <c r="D30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="4">
+        <v>1</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2010,7 +2103,10 @@
       <c r="D31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="4">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2036,9 +2132,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>12</v>
+      </c>
+      <c r="E32" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2092,9 +2191,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>12</v>
+      </c>
+      <c r="E33" s="4">
         <v>2</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2148,9 +2250,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>12</v>
+      </c>
+      <c r="E34" s="4">
         <v>3</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2204,9 +2309,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>12</v>
+      </c>
+      <c r="E35" s="4">
         <v>4</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2260,9 +2368,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>12</v>
+      </c>
+      <c r="E36" s="4">
         <v>5</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2318,7 +2429,10 @@
       <c r="D37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2374,7 +2488,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2400,9 +2517,12 @@
         </is>
       </c>
       <c r="D39" s="4">
+        <v>3</v>
+      </c>
+      <c r="E39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2463,9 +2583,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4">
         <v>2</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2528,7 +2651,10 @@
       <c r="D41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2554,9 +2680,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
         <v>1</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2627,7 +2756,10 @@
       <c r="D43" s="4">
         <v>2</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>2</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2698,7 +2830,10 @@
       <c r="D44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2767,9 +2902,12 @@
         </is>
       </c>
       <c r="D45" s="4">
+        <v>3</v>
+      </c>
+      <c r="E45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2845,9 +2983,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>2</v>
+      </c>
+      <c r="E46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2923,9 +3064,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2951,9 +3095,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>2</v>
+      </c>
+      <c r="E48" s="4">
         <v>1</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3046,7 +3193,10 @@
       <c r="D49" s="4">
         <v>2</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="4">
+        <v>2</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3137,9 +3287,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>2</v>
+      </c>
+      <c r="E50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3232,7 +3385,10 @@
       <c r="D51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3258,9 +3414,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>3</v>
+      </c>
+      <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3359,9 +3518,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>3</v>
+      </c>
+      <c r="E53" s="4">
         <v>2</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3462,7 +3624,10 @@
       <c r="D54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="4">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3568,9 +3733,12 @@
         </is>
       </c>
       <c r="D55" s="4">
+        <v>4</v>
+      </c>
+      <c r="E55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3684,9 +3852,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>4</v>
+      </c>
+      <c r="E56" s="4">
         <v>2</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3800,9 +3971,12 @@
         </is>
       </c>
       <c r="D57" s="4">
+        <v>7</v>
+      </c>
+      <c r="E57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3916,9 +4090,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>7</v>
+      </c>
+      <c r="E58" s="4">
         <v>2</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4032,9 +4209,12 @@
         </is>
       </c>
       <c r="D59" s="4">
+        <v>7</v>
+      </c>
+      <c r="E59" s="4">
         <v>3</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4148,9 +4328,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>7</v>
+      </c>
+      <c r="E60" s="4">
         <v>4</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4264,9 +4447,12 @@
         </is>
       </c>
       <c r="D61" s="4">
+        <v>58</v>
+      </c>
+      <c r="E61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4380,9 +4566,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>58</v>
+      </c>
+      <c r="E62" s="4">
         <v>2</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4496,9 +4685,12 @@
         </is>
       </c>
       <c r="D63" s="4">
+        <v>58</v>
+      </c>
+      <c r="E63" s="4">
         <v>3</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4612,9 +4804,12 @@
         </is>
       </c>
       <c r="D64" s="4">
+        <v>58</v>
+      </c>
+      <c r="E64" s="4">
         <v>4</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4728,9 +4923,12 @@
         </is>
       </c>
       <c r="D65" s="4">
+        <v>58</v>
+      </c>
+      <c r="E65" s="4">
         <v>5</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4844,9 +5042,12 @@
         </is>
       </c>
       <c r="D66" s="4">
+        <v>2</v>
+      </c>
+      <c r="E66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4902,7 +5103,10 @@
       <c r="D67" s="4">
         <v>2</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="4">
+        <v>2</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4956,9 +5160,12 @@
         </is>
       </c>
       <c r="D68" s="4">
+        <v>7</v>
+      </c>
+      <c r="E68" s="4">
         <v>1</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5012,9 +5219,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>7</v>
+      </c>
+      <c r="E69" s="4">
         <v>2</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5068,9 +5278,12 @@
         </is>
       </c>
       <c r="D70" s="4">
+        <v>7</v>
+      </c>
+      <c r="E70" s="4">
         <v>3</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5124,9 +5337,12 @@
         </is>
       </c>
       <c r="D71" s="4">
+        <v>7</v>
+      </c>
+      <c r="E71" s="4">
         <v>4</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5182,7 +5398,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5236,9 +5455,12 @@
         </is>
       </c>
       <c r="D73" s="4">
+        <v>2</v>
+      </c>
+      <c r="E73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5301,7 +5523,10 @@
       <c r="D74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5329,7 +5554,10 @@
       <c r="D75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5357,7 +5585,10 @@
       <c r="D76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5383,9 +5614,12 @@
         </is>
       </c>
       <c r="D77" s="4">
+        <v>2</v>
+      </c>
+      <c r="E77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5476,9 +5710,12 @@
         </is>
       </c>
       <c r="D78" s="4">
+        <v>2</v>
+      </c>
+      <c r="E78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5579,7 +5816,10 @@
       <c r="D79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5605,9 +5845,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5713,9 +5956,12 @@
         </is>
       </c>
       <c r="D81" s="4">
+        <v>19</v>
+      </c>
+      <c r="E81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5821,9 +6067,12 @@
         </is>
       </c>
       <c r="D82" s="4">
+        <v>19</v>
+      </c>
+      <c r="E82" s="4">
         <v>2</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5929,9 +6178,12 @@
         </is>
       </c>
       <c r="D83" s="4">
+        <v>19</v>
+      </c>
+      <c r="E83" s="4">
         <v>3</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6037,9 +6289,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>19</v>
+      </c>
+      <c r="E84" s="4">
         <v>4</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6145,9 +6400,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>19</v>
+      </c>
+      <c r="E85" s="4">
         <v>5</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6253,9 +6511,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>7</v>
+      </c>
+      <c r="E86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6369,9 +6630,12 @@
         </is>
       </c>
       <c r="D87" s="4">
+        <v>7</v>
+      </c>
+      <c r="E87" s="4">
         <v>2</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6485,9 +6749,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>7</v>
+      </c>
+      <c r="E88" s="4">
         <v>3</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6601,9 +6868,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>20</v>
+      </c>
+      <c r="E89" s="4">
         <v>1</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6717,9 +6987,12 @@
         </is>
       </c>
       <c r="D90" s="4">
+        <v>20</v>
+      </c>
+      <c r="E90" s="4">
         <v>2</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6833,9 +7106,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>20</v>
+      </c>
+      <c r="E91" s="4">
         <v>3</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6949,9 +7225,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>20</v>
+      </c>
+      <c r="E92" s="4">
         <v>4</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7065,9 +7344,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>20</v>
+      </c>
+      <c r="E93" s="4">
         <v>5</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7181,9 +7463,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>91</v>
+      </c>
+      <c r="E94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7297,9 +7582,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>91</v>
+      </c>
+      <c r="E95" s="4">
         <v>2</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7413,9 +7701,12 @@
         </is>
       </c>
       <c r="D96" s="4">
+        <v>91</v>
+      </c>
+      <c r="E96" s="4">
         <v>3</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7529,9 +7820,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>91</v>
+      </c>
+      <c r="E97" s="4">
         <v>4</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7645,9 +7939,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>91</v>
+      </c>
+      <c r="E98" s="4">
         <v>5</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7761,9 +8058,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>2</v>
+      </c>
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7817,9 +8117,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>2</v>
+      </c>
+      <c r="E100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7882,7 +8185,10 @@
       <c r="D101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="4">
+        <v>1</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7943,9 +8249,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>2</v>
+      </c>
+      <c r="E102" s="4">
         <v>1</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8016,7 +8325,10 @@
       <c r="D103" s="4">
         <v>1</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="4">
+        <v>1</v>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8087,7 +8399,10 @@
       <c r="D104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8163,9 +8478,12 @@
         </is>
       </c>
       <c r="D105" s="4">
+        <v>2</v>
+      </c>
+      <c r="E105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8243,7 +8561,10 @@
       <c r="D106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8271,7 +8592,10 @@
       <c r="D107" s="4">
         <v>1</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="4">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8364,7 +8688,10 @@
       <c r="D108" s="4">
         <v>1</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8470,9 +8797,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>5</v>
+      </c>
+      <c r="E109" s="4">
         <v>1</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8586,9 +8916,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>5</v>
+      </c>
+      <c r="E110" s="4">
         <v>2</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8702,9 +9035,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>5</v>
+      </c>
+      <c r="E111" s="4">
         <v>3</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8818,9 +9154,12 @@
         </is>
       </c>
       <c r="D112" s="4">
+        <v>3</v>
+      </c>
+      <c r="E112" s="4">
         <v>1</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8934,9 +9273,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>19</v>
+      </c>
+      <c r="E113" s="4">
         <v>1</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9050,9 +9392,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>19</v>
+      </c>
+      <c r="E114" s="4">
         <v>2</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9166,9 +9511,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>19</v>
+      </c>
+      <c r="E115" s="4">
         <v>3</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9282,9 +9630,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>19</v>
+      </c>
+      <c r="E116" s="4">
         <v>4</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9398,9 +9749,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>19</v>
+      </c>
+      <c r="E117" s="4">
         <v>5</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9514,9 +9868,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>3</v>
+      </c>
+      <c r="E118" s="4">
         <v>1</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9572,7 +9929,10 @@
       <c r="D119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9598,9 +9958,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>2</v>
+      </c>
+      <c r="E120" s="4">
         <v>1</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9671,7 +10034,10 @@
       <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9699,7 +10065,10 @@
       <c r="D122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9727,7 +10096,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9790,7 +10162,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9818,7 +10193,10 @@
       <c r="D125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9846,7 +10224,10 @@
       <c r="D126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9872,9 +10253,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>2</v>
+      </c>
+      <c r="E127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9973,9 +10357,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>2</v>
+      </c>
+      <c r="E128" s="4">
         <v>1</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10003,7 +10390,10 @@
       <c r="D129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10031,7 +10421,10 @@
       <c r="D130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="4">
+        <v>1</v>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10059,7 +10452,10 @@
       <c r="D131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="4">
+        <v>1</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10175,7 +10571,10 @@
       <c r="D132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="4">
+        <v>1</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10268,7 +10667,10 @@
       <c r="D133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E133" s="4">
+        <v>1</v>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10294,9 +10696,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>2</v>
+      </c>
+      <c r="E134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10397,7 +10802,10 @@
       <c r="D135" s="4">
         <v>2</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="4">
+        <v>2</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10498,7 +10906,10 @@
       <c r="D136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="4">
+        <v>1</v>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10619,9 +11030,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>2</v>
+      </c>
+      <c r="E137" s="4">
         <v>1</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10675,9 +11089,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>9</v>
+      </c>
+      <c r="E138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10738,9 +11155,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>9</v>
+      </c>
+      <c r="E139" s="4">
         <v>2</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10801,9 +11221,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>9</v>
+      </c>
+      <c r="E140" s="4">
         <v>3</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10864,9 +11287,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>9</v>
+      </c>
+      <c r="E141" s="4">
         <v>4</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10927,9 +11353,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>3</v>
+      </c>
+      <c r="E142" s="4">
         <v>1</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11000,7 +11429,10 @@
       <c r="D143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="4">
+        <v>1</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11093,7 +11525,10 @@
       <c r="D144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="4">
+        <v>1</v>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11186,7 +11621,10 @@
       <c r="D145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11214,7 +11652,10 @@
       <c r="D146" s="4">
         <v>1</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11240,9 +11681,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>3</v>
+      </c>
+      <c r="E147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11296,9 +11740,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>3</v>
+      </c>
+      <c r="E148" s="4">
         <v>2</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11354,7 +11801,10 @@
       <c r="D149" s="4">
         <v>3</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="4">
+        <v>3</v>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11410,7 +11860,10 @@
       <c r="D150" s="4">
         <v>1</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="4">
+        <v>1</v>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11464,9 +11917,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>2</v>
+      </c>
+      <c r="E151" s="4">
         <v>1</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11522,7 +11978,10 @@
       <c r="D152" s="4">
         <v>2</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="4">
+        <v>2</v>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11576,9 +12035,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>2</v>
+      </c>
+      <c r="E153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11634,7 +12096,10 @@
       <c r="D154" s="4">
         <v>2</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="4">
+        <v>2</v>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11688,9 +12153,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>2</v>
+      </c>
+      <c r="E155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11746,7 +12214,10 @@
       <c r="D156" s="4">
         <v>2</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="4">
+        <v>2</v>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11802,7 +12273,10 @@
       <c r="D157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="4">
+        <v>1</v>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11858,7 +12332,10 @@
       <c r="D158" s="4">
         <v>1</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="4">
+        <v>1</v>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11914,7 +12391,10 @@
       <c r="D159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="4">
+        <v>1</v>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11977,7 +12457,10 @@
       <c r="D160" s="4">
         <v>1</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="4">
+        <v>1</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12046,9 +12529,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>4</v>
+      </c>
+      <c r="E161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12109,9 +12595,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>4</v>
+      </c>
+      <c r="E162" s="4">
         <v>2</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12172,9 +12661,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>4</v>
+      </c>
+      <c r="E163" s="4">
         <v>3</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12237,7 +12729,10 @@
       <c r="D164" s="4">
         <v>4</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E164" s="4">
+        <v>4</v>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12298,9 +12793,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>22</v>
+      </c>
+      <c r="E165" s="4">
         <v>1</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12391,9 +12889,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>22</v>
+      </c>
+      <c r="E166" s="4">
         <v>2</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12477,9 +12978,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>22</v>
+      </c>
+      <c r="E167" s="4">
         <v>3</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12570,9 +13074,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>22</v>
+      </c>
+      <c r="E168" s="4">
         <v>4</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12671,9 +13178,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>22</v>
+      </c>
+      <c r="E169" s="4">
         <v>5</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12772,9 +13282,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>22</v>
+      </c>
+      <c r="E170" s="4">
         <v>6</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12873,9 +13386,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>22</v>
+      </c>
+      <c r="E171" s="4">
         <v>7</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12959,9 +13475,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>22</v>
+      </c>
+      <c r="E172" s="4">
         <v>8</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13045,9 +13564,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>22</v>
+      </c>
+      <c r="E173" s="4">
         <v>9</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13138,9 +13660,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>22</v>
+      </c>
+      <c r="E174" s="4">
         <v>10</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13231,9 +13756,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>22</v>
+      </c>
+      <c r="E175" s="4">
         <v>11</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13332,9 +13860,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>22</v>
+      </c>
+      <c r="E176" s="4">
         <v>12</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13433,9 +13964,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>22</v>
+      </c>
+      <c r="E177" s="4">
         <v>13</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13526,9 +14060,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>22</v>
+      </c>
+      <c r="E178" s="4">
         <v>14</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13619,9 +14156,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>22</v>
+      </c>
+      <c r="E179" s="4">
         <v>15</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13712,9 +14252,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>22</v>
+      </c>
+      <c r="E180" s="4">
         <v>16</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13798,9 +14341,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>22</v>
+      </c>
+      <c r="E181" s="4">
         <v>17</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13891,9 +14437,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>22</v>
+      </c>
+      <c r="E182" s="4">
         <v>18</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13999,9 +14548,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>22</v>
+      </c>
+      <c r="E183" s="4">
         <v>19</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14092,9 +14644,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>22</v>
+      </c>
+      <c r="E184" s="4">
         <v>20</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14185,9 +14740,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>3</v>
+      </c>
+      <c r="E185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14248,9 +14806,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>3</v>
+      </c>
+      <c r="E186" s="4">
         <v>2</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14313,7 +14874,10 @@
       <c r="D187" s="4">
         <v>3</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="4">
+        <v>3</v>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14376,7 +14940,10 @@
       <c r="D188" s="4">
         <v>1</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="4">
+        <v>1</v>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14447,7 +15014,10 @@
       <c r="D189" s="4">
         <v>1</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="4">
+        <v>1</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14523,9 +15093,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>2</v>
+      </c>
+      <c r="E190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14611,7 +15184,10 @@
       <c r="D191" s="4">
         <v>2</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="4">
+        <v>2</v>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14697,7 +15273,10 @@
       <c r="D192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="4">
+        <v>1</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14760,7 +15339,10 @@
       <c r="D193" s="4">
         <v>1</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="4">
+        <v>1</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14836,9 +15418,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>3</v>
+      </c>
+      <c r="E194" s="4">
         <v>1</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14908,9 +15493,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>3</v>
+      </c>
+      <c r="E195" s="4">
         <v>2</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14982,7 +15570,10 @@
       <c r="D196" s="4">
         <v>3</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="4">
+        <v>3</v>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15052,9 +15643,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>3</v>
+      </c>
+      <c r="E197" s="4">
         <v>1</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15108,9 +15702,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>3</v>
+      </c>
+      <c r="E198" s="4">
         <v>2</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15166,7 +15763,10 @@
       <c r="D199" s="4">
         <v>3</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E199" s="4">
+        <v>3</v>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15220,9 +15820,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>75</v>
+      </c>
+      <c r="E200" s="4">
         <v>1</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15276,9 +15879,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>75</v>
+      </c>
+      <c r="E201" s="4">
         <v>2</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15332,9 +15938,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>75</v>
+      </c>
+      <c r="E202" s="4">
         <v>3</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15388,9 +15997,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>75</v>
+      </c>
+      <c r="E203" s="4">
         <v>4</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15444,9 +16056,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>75</v>
+      </c>
+      <c r="E204" s="4">
         <v>5</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15500,9 +16115,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>75</v>
+      </c>
+      <c r="E205" s="4">
         <v>6</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15556,9 +16174,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>75</v>
+      </c>
+      <c r="E206" s="4">
         <v>7</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15612,9 +16233,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>75</v>
+      </c>
+      <c r="E207" s="4">
         <v>8</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15668,9 +16292,12 @@
         </is>
       </c>
       <c r="D208" s="4">
+        <v>75</v>
+      </c>
+      <c r="E208" s="4">
         <v>9</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15724,9 +16351,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>75</v>
+      </c>
+      <c r="E209" s="4">
         <v>10</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15780,9 +16410,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>75</v>
+      </c>
+      <c r="E210" s="4">
         <v>11</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15836,9 +16469,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>75</v>
+      </c>
+      <c r="E211" s="4">
         <v>12</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15892,9 +16528,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>75</v>
+      </c>
+      <c r="E212" s="4">
         <v>13</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15948,9 +16587,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>75</v>
+      </c>
+      <c r="E213" s="4">
         <v>14</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16004,9 +16646,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>75</v>
+      </c>
+      <c r="E214" s="4">
         <v>15</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16060,9 +16705,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>75</v>
+      </c>
+      <c r="E215" s="4">
         <v>16</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16116,9 +16764,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>75</v>
+      </c>
+      <c r="E216" s="4">
         <v>17</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16172,9 +16823,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>75</v>
+      </c>
+      <c r="E217" s="4">
         <v>18</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16228,9 +16882,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>75</v>
+      </c>
+      <c r="E218" s="4">
         <v>19</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16284,9 +16941,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>75</v>
+      </c>
+      <c r="E219" s="4">
         <v>20</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16342,7 +17002,10 @@
       <c r="D220" s="4">
         <v>1</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="4">
+        <v>1</v>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16412,9 +17075,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>2</v>
+      </c>
+      <c r="E221" s="4">
         <v>1</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16515,7 +17181,10 @@
       <c r="D222" s="4">
         <v>2</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="E222" s="4">
+        <v>2</v>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16623,7 +17292,10 @@
       <c r="D223" s="4">
         <v>1</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="E223" s="4">
+        <v>1</v>
+      </c>
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16724,7 +17396,10 @@
       <c r="D224" s="4">
         <v>1</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="E224" s="4">
+        <v>1</v>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16785,9 +17460,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>6</v>
+      </c>
+      <c r="E225" s="4">
         <v>1</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16848,9 +17526,12 @@
         </is>
       </c>
       <c r="D226" s="4">
+        <v>6</v>
+      </c>
+      <c r="E226" s="4">
         <v>2</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16911,9 +17592,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>6</v>
+      </c>
+      <c r="E227" s="4">
         <v>3</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16974,9 +17658,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>6</v>
+      </c>
+      <c r="E228" s="4">
         <v>4</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17037,9 +17724,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>6</v>
+      </c>
+      <c r="E229" s="4">
         <v>5</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17102,7 +17792,10 @@
       <c r="D230" s="4">
         <v>6</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E230" s="4">
+        <v>6</v>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17163,9 +17856,12 @@
         </is>
       </c>
       <c r="D231" s="4">
+        <v>5</v>
+      </c>
+      <c r="E231" s="4">
         <v>1</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17235,9 +17931,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>5</v>
+      </c>
+      <c r="E232" s="4">
         <v>2</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17307,9 +18006,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>5</v>
+      </c>
+      <c r="E233" s="4">
         <v>3</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17379,9 +18081,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>5</v>
+      </c>
+      <c r="E234" s="4">
         <v>4</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17453,7 +18158,10 @@
       <c r="D235" s="4">
         <v>5</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="E235" s="4">
+        <v>5</v>
+      </c>
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17525,7 +18233,10 @@
       <c r="D236" s="4">
         <v>1</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E236" s="4">
+        <v>1</v>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17597,7 +18308,10 @@
       <c r="D237" s="4">
         <v>1</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="4">
+        <v>1</v>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17667,9 +18381,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>2</v>
+      </c>
+      <c r="E238" s="4">
         <v>1</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17741,7 +18458,10 @@
       <c r="D239" s="4">
         <v>2</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="4">
+        <v>2</v>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17813,7 +18533,10 @@
       <c r="D240" s="4">
         <v>1</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="4">
+        <v>1</v>
+      </c>
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17885,7 +18608,10 @@
       <c r="D241" s="4">
         <v>1</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="4">
+        <v>1</v>
+      </c>
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17957,7 +18683,10 @@
       <c r="D242" s="4">
         <v>1</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="4">
+        <v>1</v>
+      </c>
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18027,9 +18756,12 @@
         </is>
       </c>
       <c r="D243" s="4">
+        <v>3</v>
+      </c>
+      <c r="E243" s="4">
         <v>1</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18099,9 +18831,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>3</v>
+      </c>
+      <c r="E244" s="4">
         <v>2</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18173,7 +18908,10 @@
       <c r="D245" s="4">
         <v>3</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E245" s="4">
+        <v>3</v>
+      </c>
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18245,7 +18983,10 @@
       <c r="D246" s="4">
         <v>1</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E246" s="4">
+        <v>1</v>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18317,7 +19058,10 @@
       <c r="D247" s="4">
         <v>1</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="E247" s="4">
+        <v>1</v>
+      </c>
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18389,7 +19133,10 @@
       <c r="D248" s="4">
         <v>1</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="E248" s="4">
+        <v>1</v>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18459,9 +19206,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>3</v>
+      </c>
+      <c r="E249" s="4">
         <v>1</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18531,9 +19281,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>3</v>
+      </c>
+      <c r="E250" s="4">
         <v>2</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18605,7 +19358,10 @@
       <c r="D251" s="4">
         <v>3</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E251" s="4">
+        <v>3</v>
+      </c>
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18659,127 +19415,167 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="120">
+  <mergeCells count="160">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:D17"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="B23:B27"/>
     <mergeCell ref="C23:C27"/>
+    <mergeCell ref="D23:D27"/>
     <mergeCell ref="A32:A36"/>
     <mergeCell ref="B32:B36"/>
     <mergeCell ref="C32:C36"/>
+    <mergeCell ref="D32:D36"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="B55:B56"/>
     <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
     <mergeCell ref="A57:A60"/>
     <mergeCell ref="B57:B60"/>
     <mergeCell ref="C57:C60"/>
+    <mergeCell ref="D57:D60"/>
     <mergeCell ref="A61:A65"/>
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="B66:B67"/>
     <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
     <mergeCell ref="A68:A71"/>
     <mergeCell ref="B68:B71"/>
     <mergeCell ref="C68:C71"/>
+    <mergeCell ref="D68:D71"/>
     <mergeCell ref="A81:A85"/>
     <mergeCell ref="B81:B85"/>
     <mergeCell ref="C81:C85"/>
+    <mergeCell ref="D81:D85"/>
     <mergeCell ref="A86:A88"/>
     <mergeCell ref="B86:B88"/>
     <mergeCell ref="C86:C88"/>
+    <mergeCell ref="D86:D88"/>
     <mergeCell ref="A89:A93"/>
     <mergeCell ref="B89:B93"/>
     <mergeCell ref="C89:C93"/>
+    <mergeCell ref="D89:D93"/>
     <mergeCell ref="A94:A98"/>
     <mergeCell ref="B94:B98"/>
     <mergeCell ref="C94:C98"/>
+    <mergeCell ref="D94:D98"/>
     <mergeCell ref="A109:A111"/>
     <mergeCell ref="B109:B111"/>
     <mergeCell ref="C109:C111"/>
+    <mergeCell ref="D109:D111"/>
     <mergeCell ref="A113:A117"/>
     <mergeCell ref="B113:B117"/>
     <mergeCell ref="C113:C117"/>
+    <mergeCell ref="D113:D117"/>
     <mergeCell ref="A134:A135"/>
     <mergeCell ref="B134:B135"/>
     <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
     <mergeCell ref="A138:A141"/>
     <mergeCell ref="B138:B141"/>
     <mergeCell ref="C138:C141"/>
+    <mergeCell ref="D138:D141"/>
     <mergeCell ref="A147:A149"/>
     <mergeCell ref="B147:B149"/>
     <mergeCell ref="C147:C149"/>
+    <mergeCell ref="D147:D149"/>
     <mergeCell ref="A151:A152"/>
     <mergeCell ref="B151:B152"/>
     <mergeCell ref="C151:C152"/>
+    <mergeCell ref="D151:D152"/>
     <mergeCell ref="A153:A154"/>
     <mergeCell ref="B153:B154"/>
     <mergeCell ref="C153:C154"/>
+    <mergeCell ref="D153:D154"/>
     <mergeCell ref="A155:A156"/>
     <mergeCell ref="B155:B156"/>
     <mergeCell ref="C155:C156"/>
+    <mergeCell ref="D155:D156"/>
     <mergeCell ref="A161:A164"/>
     <mergeCell ref="B161:B164"/>
     <mergeCell ref="C161:C164"/>
+    <mergeCell ref="D161:D164"/>
     <mergeCell ref="A165:A184"/>
     <mergeCell ref="B165:B184"/>
     <mergeCell ref="C165:C184"/>
+    <mergeCell ref="D165:D184"/>
     <mergeCell ref="A185:A187"/>
     <mergeCell ref="B185:B187"/>
     <mergeCell ref="C185:C187"/>
+    <mergeCell ref="D185:D187"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="B190:B191"/>
     <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
     <mergeCell ref="A194:A196"/>
     <mergeCell ref="B194:B196"/>
     <mergeCell ref="C194:C196"/>
+    <mergeCell ref="D194:D196"/>
     <mergeCell ref="A197:A199"/>
     <mergeCell ref="B197:B199"/>
     <mergeCell ref="C197:C199"/>
+    <mergeCell ref="D197:D199"/>
     <mergeCell ref="A200:A219"/>
     <mergeCell ref="B200:B219"/>
     <mergeCell ref="C200:C219"/>
+    <mergeCell ref="D200:D219"/>
     <mergeCell ref="A221:A222"/>
     <mergeCell ref="B221:B222"/>
     <mergeCell ref="C221:C222"/>
+    <mergeCell ref="D221:D222"/>
     <mergeCell ref="A225:A230"/>
     <mergeCell ref="B225:B230"/>
     <mergeCell ref="C225:C230"/>
+    <mergeCell ref="D225:D230"/>
     <mergeCell ref="A231:A235"/>
     <mergeCell ref="B231:B235"/>
     <mergeCell ref="C231:C235"/>
+    <mergeCell ref="D231:D235"/>
     <mergeCell ref="A238:A239"/>
     <mergeCell ref="B238:B239"/>
     <mergeCell ref="C238:C239"/>
+    <mergeCell ref="D238:D239"/>
     <mergeCell ref="A243:A245"/>
     <mergeCell ref="B243:B245"/>
     <mergeCell ref="C243:C245"/>
+    <mergeCell ref="D243:D245"/>
     <mergeCell ref="A249:A251"/>
     <mergeCell ref="B249:B251"/>
     <mergeCell ref="C249:C251"/>
+    <mergeCell ref="D249:D251"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
